--- a/Result/profitability/8271.xlsx
+++ b/Result/profitability/8271.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.66</v>
       </c>
       <c r="M2" t="n">
-        <v>2.64375</v>
+        <v>5.225</v>
       </c>
       <c r="N2" t="n">
-        <v>20.17</v>
+        <v>24.71375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.87</v>
       </c>
       <c r="M3" t="n">
-        <v>2.7175</v>
+        <v>5.297499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>19.49875</v>
+        <v>24.3325</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.02</v>
       </c>
       <c r="M4" t="n">
-        <v>2.80875</v>
+        <v>5.335</v>
       </c>
       <c r="N4" t="n">
-        <v>19.5375</v>
+        <v>23.88375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.34</v>
       </c>
       <c r="M5" t="n">
-        <v>2.76125</v>
+        <v>5.25</v>
       </c>
       <c r="N5" t="n">
-        <v>18.58375</v>
+        <v>23.065</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>2.70875</v>
+        <v>5.11125</v>
       </c>
       <c r="N6" t="n">
-        <v>17.5425</v>
+        <v>21.64875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.82</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5975</v>
+        <v>4.8075</v>
       </c>
       <c r="N7" t="n">
-        <v>16.2575</v>
+        <v>18.84375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.31</v>
       </c>
       <c r="M8" t="n">
-        <v>2.355</v>
+        <v>3.15375</v>
       </c>
       <c r="N8" t="n">
-        <v>13.56</v>
+        <v>13.8075</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9572,6 +9572,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>9676</v>
+      </c>
+      <c r="D73" t="n">
+        <v>4717</v>
+      </c>
+      <c r="E73" t="n">
+        <v>4959</v>
+      </c>
+      <c r="F73" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="G73" t="n">
+        <v>3494</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>36.11%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>-33</v>
+      </c>
+      <c r="J73" t="n">
+        <v>3461</v>
+      </c>
+      <c r="K73" t="n">
+        <v>2713</v>
+      </c>
+      <c r="L73" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="M73" t="n">
+        <v>5.342499999999999</v>
+      </c>
+      <c r="N73" t="n">
+        <v>26.105</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>6.390000000000001</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0.4394773039889959</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>1.979999999999997</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.04018672620255725</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>19.51960784313725</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>35.85</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>2.327922077922078</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
